--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6544A6-4222-45AB-9513-D25C4D5BE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB1E56F-139F-4EF7-921E-8B0B44DE8E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-46188" yWindow="-2688" windowWidth="23256" windowHeight="14016" activeTab="2" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB1E56F-139F-4EF7-921E-8B0B44DE8E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE539E45-6009-4076-9577-E8BDCDC038CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-46188" yWindow="-2688" windowWidth="23256" windowHeight="14016" activeTab="2" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -486,9 +486,6 @@
     <t>Percentag of energy captured through POD modes</t>
   </si>
   <si>
-    <t>eng</t>
-  </si>
-  <si>
     <t>Number of POD modes.</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>stride</t>
+  </si>
+  <si>
+    <t>Emax</t>
   </si>
 </sst>
 </file>
@@ -1947,16 +1947,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>166</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>167</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>49</v>
@@ -1970,16 +1970,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>49</v>
@@ -2295,7 +2295,7 @@
         <v>48</v>
       </c>
       <c r="F2" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>16</v>
@@ -2691,7 +2691,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
@@ -2714,7 +2714,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
@@ -2737,7 +2737,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="39" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>158</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>159</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>48</v>
@@ -2783,7 +2783,7 @@
         <v>63</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>60</v>
@@ -2800,16 +2800,16 @@
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" s="39" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="39" t="s">
         <v>190</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>191</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>48</v>
@@ -2832,7 +2832,7 @@
         <v>136</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>48</v>
@@ -2855,7 +2855,7 @@
         <v>137</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>55</v>
@@ -3030,13 +3030,13 @@
     </row>
     <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>134</v>
@@ -3059,7 +3059,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>127</v>
@@ -3099,13 +3099,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="C20" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>172</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>127</v>
@@ -3122,16 +3122,16 @@
     </row>
     <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>48</v>
@@ -3143,16 +3143,16 @@
     </row>
     <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="26" t="s">
         <v>175</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>176</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>47</v>
@@ -3166,16 +3166,16 @@
     </row>
     <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>48</v>
@@ -3189,16 +3189,16 @@
     </row>
     <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B24" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="D24" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>48</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="25" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>48</v>
@@ -3235,16 +3235,16 @@
     </row>
     <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="28" t="s">
         <v>199</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>200</v>
       </c>
       <c r="E26" s="28" t="s">
         <v>47</v>
@@ -3258,16 +3258,16 @@
     </row>
     <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E27" s="26" t="s">
         <v>49</v>
@@ -3281,13 +3281,13 @@
     </row>
     <row r="28" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>20</v>
@@ -3304,16 +3304,16 @@
     </row>
     <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>48</v>
@@ -3327,16 +3327,16 @@
     </row>
     <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>49</v>
@@ -3350,16 +3350,16 @@
     </row>
     <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>49</v>
@@ -3373,16 +3373,16 @@
     </row>
     <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>48</v>
@@ -3396,16 +3396,16 @@
     </row>
     <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>49</v>
@@ -3419,16 +3419,16 @@
     </row>
     <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>207</v>
-      </c>
       <c r="C34" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D34" s="26" t="s">
         <v>221</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>222</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>48</v>
@@ -3442,16 +3442,16 @@
     </row>
     <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" s="26" t="s">
         <v>223</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>224</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>48</v>
@@ -3465,16 +3465,16 @@
     </row>
     <row r="36" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>225</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>226</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>48</v>
@@ -3488,16 +3488,16 @@
     </row>
     <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D37" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>48</v>
@@ -3511,16 +3511,16 @@
     </row>
     <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E38" s="26" t="s">
         <v>48</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="39" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D39" s="27" t="s">
         <v>227</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>228</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>48</v>
@@ -3820,10 +3820,10 @@
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>155</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>156</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>55</v>
@@ -3843,10 +3843,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>49</v>
@@ -3855,21 +3855,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>162</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>163</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>49</v>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3889,10 +3889,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>102</v>
@@ -3901,7 +3901,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -3912,10 +3912,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -3935,10 +3935,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>146</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>147</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>48</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE539E45-6009-4076-9577-E8BDCDC038CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{AE539E45-6009-4076-9577-E8BDCDC038CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC872CD8-C2CB-4FAE-80DF-AB1D6F2749C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1372,7 +1372,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1387,10 +1387,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1428,7 +1432,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1534,7 +1538,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1676,7 +1680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1685,17 +1689,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1703,7 +1707,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1711,7 +1715,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1719,7 +1723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1727,8 +1731,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1753,7 +1757,7 @@
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1782,7 +1786,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1794,7 +1798,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1806,7 +1810,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1818,7 +1822,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1845,15 +1849,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1876,7 +1880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>89</v>
       </c>
@@ -1893,13 +1897,13 @@
         <v>107</v>
       </c>
       <c r="F2" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>90</v>
       </c>
@@ -1922,7 +1926,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>91</v>
       </c>
@@ -1939,13 +1943,13 @@
         <v>49</v>
       </c>
       <c r="F4" s="11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>163</v>
       </c>
@@ -1968,7 +1972,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>164</v>
       </c>
@@ -1991,7 +1995,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
@@ -2014,7 +2018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -2023,7 +2027,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -2032,7 +2036,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -2041,7 +2045,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -2050,7 +2054,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -2059,7 +2063,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -2068,7 +2072,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -2077,7 +2081,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -2086,7 +2090,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -2095,7 +2099,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -2104,7 +2108,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -2113,7 +2117,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -2122,7 +2126,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -2131,7 +2135,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -2140,7 +2144,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -2149,7 +2153,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -2158,7 +2162,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -2167,7 +2171,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -2176,7 +2180,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2185,7 +2189,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2194,7 +2198,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2203,7 +2207,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2212,7 +2216,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2247,15 +2251,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>93</v>
       </c>
@@ -2301,7 +2305,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>94</v>
       </c>
@@ -2324,7 +2328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>97</v>
       </c>
@@ -2347,7 +2351,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>109</v>
       </c>
@@ -2370,7 +2374,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>110</v>
       </c>
@@ -2393,7 +2397,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>111</v>
       </c>
@@ -2416,7 +2420,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>112</v>
       </c>
@@ -2439,7 +2443,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>113</v>
       </c>
@@ -2462,7 +2466,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>114</v>
       </c>
@@ -2485,7 +2489,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="25"/>
       <c r="C11" s="5"/>
@@ -2494,7 +2498,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2503,7 +2507,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2512,7 +2516,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2521,7 +2525,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2530,7 +2534,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2539,7 +2543,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2548,7 +2552,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2557,7 +2561,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2566,7 +2570,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2575,7 +2579,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2584,7 +2588,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2593,7 +2597,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2602,7 +2606,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2611,7 +2615,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2620,7 +2624,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2651,16 +2655,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2683,7 +2687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2706,7 +2710,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2729,7 +2733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2752,7 +2756,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>156</v>
       </c>
@@ -2775,7 +2779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2798,7 +2802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>188</v>
       </c>
@@ -2821,7 +2825,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>81</v>
       </c>
@@ -2844,7 +2848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
@@ -2867,7 +2871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>72</v>
       </c>
@@ -2890,7 +2894,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
@@ -2913,7 +2917,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
@@ -2936,7 +2940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>73</v>
       </c>
@@ -2959,7 +2963,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>74</v>
       </c>
@@ -2982,7 +2986,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -3005,7 +3009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>76</v>
       </c>
@@ -3028,7 +3032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>168</v>
       </c>
@@ -3051,7 +3055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>79</v>
       </c>
@@ -3074,7 +3078,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
@@ -3097,7 +3101,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>169</v>
       </c>
@@ -3120,7 +3124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>172</v>
       </c>
@@ -3141,7 +3145,7 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>173</v>
       </c>
@@ -3164,7 +3168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>178</v>
       </c>
@@ -3187,7 +3191,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>179</v>
       </c>
@@ -3210,7 +3214,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>180</v>
       </c>
@@ -3233,7 +3237,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>192</v>
       </c>
@@ -3256,7 +3260,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>193</v>
       </c>
@@ -3279,7 +3283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>194</v>
       </c>
@@ -3302,7 +3306,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>200</v>
       </c>
@@ -3325,7 +3329,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>201</v>
       </c>
@@ -3348,7 +3352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>202</v>
       </c>
@@ -3371,7 +3375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>203</v>
       </c>
@@ -3394,7 +3398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>204</v>
       </c>
@@ -3417,7 +3421,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>205</v>
       </c>
@@ -3440,7 +3444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>207</v>
       </c>
@@ -3463,7 +3467,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>208</v>
       </c>
@@ -3486,7 +3490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="38" t="s">
         <v>228</v>
       </c>
@@ -3509,7 +3513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38" t="s">
         <v>229</v>
       </c>
@@ -3532,7 +3536,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>209</v>
       </c>
@@ -3555,7 +3559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
       <c r="B40" s="28"/>
       <c r="C40" s="8"/>
@@ -3564,7 +3568,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="31"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3573,7 +3577,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3582,7 +3586,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="26"/>
       <c r="C43" s="5"/>
@@ -3643,15 +3647,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3674,7 +3678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3697,7 +3701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3720,7 +3724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3743,7 +3747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3766,7 +3770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3789,7 +3793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3812,7 +3816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3835,7 +3839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3858,7 +3862,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>160</v>
       </c>
@@ -3881,7 +3885,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>86</v>
       </c>
@@ -3904,7 +3908,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>87</v>
       </c>
@@ -3927,7 +3931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>88</v>
       </c>
@@ -3950,7 +3954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3959,7 +3963,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3968,7 +3972,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3977,7 +3981,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3986,7 +3990,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3995,7 +3999,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -4004,7 +4008,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -4013,7 +4017,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -4022,7 +4026,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -4031,7 +4035,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -4040,7 +4044,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -4049,7 +4053,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -4058,7 +4062,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{AE539E45-6009-4076-9577-E8BDCDC038CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC872CD8-C2CB-4FAE-80DF-AB1D6F2749C6}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{AE539E45-6009-4076-9577-E8BDCDC038CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF61534-C8AF-490B-A8A7-5D0E6A1B4170}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -2368,7 +2368,7 @@
         <v>102</v>
       </c>
       <c r="F5" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="29" t="s">
         <v>103</v>
@@ -2391,7 +2391,7 @@
         <v>102</v>
       </c>
       <c r="F6" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="29" t="s">
         <v>103</v>
@@ -2437,7 +2437,7 @@
         <v>102</v>
       </c>
       <c r="F8" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="29" t="s">
         <v>103</v>
@@ -2460,7 +2460,7 @@
         <v>102</v>
       </c>
       <c r="F9" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="29" t="s">
         <v>103</v>
@@ -3072,7 +3072,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{AE539E45-6009-4076-9577-E8BDCDC038CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF61534-C8AF-490B-A8A7-5D0E6A1B4170}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35130DA7-98BF-4B53-BE58-382DA215F377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1372,7 +1372,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1387,14 +1387,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1432,7 +1428,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1538,7 +1534,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1680,7 +1676,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1689,17 +1685,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1707,7 +1703,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1715,7 +1711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1723,7 +1719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1731,8 +1727,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1753,7 @@
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
-    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1786,7 +1782,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1798,7 +1794,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1810,7 +1806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1822,7 +1818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1849,15 +1845,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1880,7 +1876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>89</v>
       </c>
@@ -1903,7 +1899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>90</v>
       </c>
@@ -1926,7 +1922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>91</v>
       </c>
@@ -1949,7 +1945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>163</v>
       </c>
@@ -1972,7 +1968,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>164</v>
       </c>
@@ -1995,7 +1991,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
@@ -2018,7 +2014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -2027,7 +2023,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -2036,7 +2032,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -2045,7 +2041,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -2054,7 +2050,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -2063,7 +2059,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -2072,7 +2068,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -2081,7 +2077,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -2090,7 +2086,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -2099,7 +2095,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -2108,7 +2104,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -2117,7 +2113,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -2126,7 +2122,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -2135,7 +2131,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -2144,7 +2140,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -2153,7 +2149,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -2162,7 +2158,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -2171,7 +2167,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -2180,7 +2176,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2189,7 +2185,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2198,7 +2194,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2207,7 +2203,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2216,7 +2212,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2251,15 +2247,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2282,7 +2278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>93</v>
       </c>
@@ -2305,7 +2301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>94</v>
       </c>
@@ -2328,7 +2324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>97</v>
       </c>
@@ -2351,7 +2347,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>109</v>
       </c>
@@ -2374,7 +2370,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>110</v>
       </c>
@@ -2397,7 +2393,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>111</v>
       </c>
@@ -2420,7 +2416,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>112</v>
       </c>
@@ -2443,7 +2439,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>113</v>
       </c>
@@ -2466,7 +2462,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>114</v>
       </c>
@@ -2489,7 +2485,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="25"/>
       <c r="C11" s="5"/>
@@ -2498,7 +2494,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2507,7 +2503,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2516,7 +2512,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2525,7 +2521,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2534,7 +2530,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2543,7 +2539,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2552,7 +2548,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2561,7 +2557,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2570,7 +2566,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2579,7 +2575,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2588,7 +2584,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2597,7 +2593,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2606,7 +2602,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2615,7 +2611,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2624,7 +2620,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2655,16 +2651,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2687,7 +2683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2710,7 +2706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2733,7 +2729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2756,7 +2752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
         <v>156</v>
       </c>
@@ -2779,7 +2775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2802,7 +2798,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
         <v>188</v>
       </c>
@@ -2825,7 +2821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>81</v>
       </c>
@@ -2848,7 +2844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
@@ -2871,7 +2867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>72</v>
       </c>
@@ -2894,7 +2890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
@@ -2917,7 +2913,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
@@ -2940,7 +2936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>73</v>
       </c>
@@ -2963,7 +2959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>74</v>
       </c>
@@ -2986,7 +2982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -3009,7 +3005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>76</v>
       </c>
@@ -3032,7 +3028,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>168</v>
       </c>
@@ -3055,7 +3051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>79</v>
       </c>
@@ -3072,13 +3068,13 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
@@ -3101,7 +3097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>169</v>
       </c>
@@ -3124,7 +3120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>172</v>
       </c>
@@ -3145,7 +3141,7 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>173</v>
       </c>
@@ -3168,7 +3164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>178</v>
       </c>
@@ -3191,7 +3187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>179</v>
       </c>
@@ -3214,7 +3210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>180</v>
       </c>
@@ -3237,7 +3233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>192</v>
       </c>
@@ -3260,7 +3256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>193</v>
       </c>
@@ -3283,7 +3279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>194</v>
       </c>
@@ -3306,7 +3302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>200</v>
       </c>
@@ -3329,7 +3325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>201</v>
       </c>
@@ -3352,7 +3348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>202</v>
       </c>
@@ -3375,7 +3371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>203</v>
       </c>
@@ -3398,7 +3394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>204</v>
       </c>
@@ -3421,7 +3417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>205</v>
       </c>
@@ -3444,7 +3440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>207</v>
       </c>
@@ -3467,7 +3463,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>208</v>
       </c>
@@ -3490,7 +3486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>228</v>
       </c>
@@ -3513,7 +3509,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
         <v>229</v>
       </c>
@@ -3536,7 +3532,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>209</v>
       </c>
@@ -3559,7 +3555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="28"/>
       <c r="C40" s="8"/>
@@ -3568,7 +3564,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="31"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3577,7 +3573,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3586,7 +3582,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="26"/>
       <c r="C43" s="5"/>
@@ -3647,15 +3643,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3678,7 +3674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3701,7 +3697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3724,7 +3720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3747,7 +3743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3770,7 +3766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3793,7 +3789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3816,7 +3812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3839,7 +3835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3862,7 +3858,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>160</v>
       </c>
@@ -3885,7 +3881,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>86</v>
       </c>
@@ -3908,7 +3904,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>87</v>
       </c>
@@ -3931,7 +3927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>88</v>
       </c>
@@ -3954,7 +3950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3963,7 +3959,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3972,7 +3968,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3981,7 +3977,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3990,7 +3986,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3999,7 +3995,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -4008,7 +4004,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -4017,7 +4013,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -4026,7 +4022,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -4035,7 +4031,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -4044,7 +4040,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -4053,7 +4049,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -4062,7 +4058,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35130DA7-98BF-4B53-BE58-382DA215F377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E21A68-2961-4C4B-980B-5279775D5C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -3068,7 +3068,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E21A68-2961-4C4B-980B-5279775D5C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9070D7FA-E496-4A80-A7E6-6105BC41D368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1685,17 +1685,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1727,8 +1727,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1753,7 +1753,7 @@
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1845,15 +1845,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>89</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>90</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>91</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>163</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>164</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -2023,7 +2023,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -2032,7 +2032,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -2041,7 +2041,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -2050,7 +2050,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -2059,7 +2059,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -2068,7 +2068,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -2077,7 +2077,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -2086,7 +2086,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -2095,7 +2095,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -2104,7 +2104,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -2113,7 +2113,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -2122,7 +2122,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -2131,7 +2131,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -2140,7 +2140,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -2149,7 +2149,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -2158,7 +2158,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -2167,7 +2167,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -2176,7 +2176,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2185,7 +2185,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2194,7 +2194,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2203,7 +2203,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2212,7 +2212,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2247,15 +2247,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>93</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>94</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>97</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>109</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>110</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>111</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>112</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>113</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>114</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="25"/>
       <c r="C11" s="5"/>
@@ -2494,7 +2494,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2503,7 +2503,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2512,7 +2512,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2521,7 +2521,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2530,7 +2530,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2539,7 +2539,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2548,7 +2548,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2557,7 +2557,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2566,7 +2566,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2575,7 +2575,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2584,7 +2584,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2593,7 +2593,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2602,7 +2602,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2611,7 +2611,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2620,7 +2620,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2651,16 +2651,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>156</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>188</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>81</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>72</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>73</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>74</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>76</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>168</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>79</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>169</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>172</v>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>173</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>178</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>179</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>180</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>192</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>193</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>194</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>200</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>201</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>202</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>203</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>204</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>205</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>207</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>208</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="38" t="s">
         <v>228</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38" t="s">
         <v>229</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>209</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
       <c r="B40" s="28"/>
       <c r="C40" s="8"/>
@@ -3564,7 +3564,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="31"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3573,7 +3573,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3582,7 +3582,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="26"/>
       <c r="C43" s="5"/>
@@ -3643,15 +3643,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>160</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>86</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>87</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>88</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3959,7 +3959,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3968,7 +3968,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3977,7 +3977,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3986,7 +3986,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3995,7 +3995,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -4004,7 +4004,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -4013,7 +4013,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -4022,7 +4022,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -4031,7 +4031,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -4040,7 +4040,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -4049,7 +4049,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -4058,7 +4058,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9070D7FA-E496-4A80-A7E6-6105BC41D368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -3068,7 +3068,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77CB4535-E0E1-4BE2-A0A4-ED31ECD8F0C0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="3456" yWindow="3456" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1372,7 +1372,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1388,9 +1388,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1428,7 +1428,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1534,7 +1534,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1676,7 +1676,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1685,7 +1685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
@@ -1845,7 +1845,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
@@ -2247,7 +2247,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" customWidth="1"/>
@@ -2651,7 +2651,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
@@ -3068,7 +3068,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>
@@ -3643,7 +3643,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77CB4535-E0E1-4BE2-A0A4-ED31ECD8F0C0}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0757C2E0-9A08-414A-832B-6C3DB3730E80}"/>
   <bookViews>
-    <workbookView xWindow="3456" yWindow="3456" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1385,6 +1385,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0757C2E0-9A08-414A-832B-6C3DB3730E80}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{679A95A5-206A-4E9C-8B04-523A8D45DA79}"/>
   <bookViews>
     <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -3072,7 +3072,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{679A95A5-206A-4E9C-8B04-523A8D45DA79}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EB8C427-E98D-4DDA-AC8E-81B3BEB12B12}"/>
   <bookViews>
     <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -3072,7 +3072,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EB8C427-E98D-4DDA-AC8E-81B3BEB12B12}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{343DBD66-5C29-4283-81BC-F4DBCFD74DE4}"/>
   <bookViews>
-    <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{343DBD66-5C29-4283-81BC-F4DBCFD74DE4}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8BFD24-9D5E-4CE9-A48D-6FEB98AD1097}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8BFD24-9D5E-4CE9-A48D-6FEB98AD1097}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7FD5201-55E6-4324-8ED1-62BBBCC4A011}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -3072,7 +3072,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7FD5201-55E6-4324-8ED1-62BBBCC4A011}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B51CA3D-7F2D-4563-AB1A-AB8D35A469E3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -3072,7 +3072,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/default2D.xlsx
+++ b/config/default2D.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schir\OneDrive\Studium\34_Github\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B51CA3D-7F2D-4563-AB1A-AB8D35A469E3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B40676-7B6B-4D44-AA0E-A3BFA33FB4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="260">
   <si>
     <t>#</t>
   </si>
@@ -798,6 +798,91 @@
   </si>
   <si>
     <t>Emax</t>
+  </si>
+  <si>
+    <t>BasisFunction</t>
+  </si>
+  <si>
+    <t>gpr</t>
+  </si>
+  <si>
+    <t>Explicit basis in the GPR model:
+1) Constant
+2) Linear
+3) Quadratic</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>Form of the covariance function, specified as one of the following:
+1) Exponential
+2) Squareexponential</t>
+  </si>
+  <si>
+    <t>IterationLimit</t>
+  </si>
+  <si>
+    <t>Maximum number of block coordinate descent method ("bcd") iterations.</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>Ensemble aggregation method:
+1) LSBoost
+2) Bag</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>LearningCycles</t>
+  </si>
+  <si>
+    <t>Number of ensemble learning cycles</t>
+  </si>
+  <si>
+    <t>cycle</t>
+  </si>
+  <si>
+    <t>nn</t>
+  </si>
+  <si>
+    <t>Maximum number of training iterations</t>
+  </si>
+  <si>
+    <t>NumberLayers</t>
+  </si>
+  <si>
+    <t>Number of fully connected layers in the network.</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>NumberNeurons</t>
+  </si>
+  <si>
+    <t>Number of nodes per fully connected layer.</t>
+  </si>
+  <si>
+    <t>nodes</t>
+  </si>
+  <si>
+    <t>Activation</t>
+  </si>
+  <si>
+    <t>Activation functions for the fully connected layers of the neural network model:
+1) relu
+2) tanh
+3) sigmoid</t>
+  </si>
+  <si>
+    <t>act</t>
   </si>
 </sst>
 </file>
@@ -1385,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2654,7 +2735,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -3559,54 +3640,284 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="31"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="29"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="29"/>
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="48">
+        <v>1</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="6">
+        <v>1</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="10">
+        <v>100</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="6">
+        <v>100</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="10">
+        <v>50</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" s="9">
+        <v>100</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="6">
+        <v>50</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="29"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="29"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="13"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="29"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F50:F53" xr:uid="{71700759-FDA6-46F1-B8C0-9D577C0177B9}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F38" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21 F41 F43" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36 F40 F49 F47" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3630,7 +3941,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39 F44:F46 F42 F48" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
